--- a/task256/golden/workstation_configurations_2027.xlsx
+++ b/task256/golden/workstation_configurations_2027.xlsx
@@ -29,10 +29,10 @@
     <t>Tamarack Valley Regional Transit Authority</t>
   </si>
   <si>
-    <t>Specify Configuration G for the 2027 order: the lowest-priced configuration that fits at least 95 per cent of our bus operators (96.4 per cent, $4,450 per bus)</t>
-  </si>
-  <si>
-    <t>Standard ES-12, section 3; the 2,110 bus operators on the roster of 30 September 2026 at their latest DOT physical; envelopes and prices from Halvard's fit report of 28 August 2026; body dimensions from the Survey of Working Adults' Body Dimensions (2012), within sex.</t>
+    <t>Specify Configuration H for the 2027 order: the lowest-priced configuration that fits at least 95 per cent of our bus operators (97.0 per cent, $5,900 per bus)</t>
+  </si>
+  <si>
+    <t>Standard ES-12, section 3; the 2,110 bus operators on the roster of 30 September 2026 at their latest DOT physical; envelopes and prices from Halvard's fit report of 28 August 2026; body dimensions from the Survey of Working Adults' Body Dimensions (2012), within sex, moved to the operators Halvard measured in August 2026.</t>
   </si>
   <si>
     <t>Configuration</t>
@@ -98,15 +98,15 @@
     <t>Power-adjustable pedal set; Extended-range seat riser; Tilt-telescope steering column; Deep-travel seat track</t>
   </si>
   <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>Power-adjustable pedal set; Extended-range seat riser; Tilt-telescope steering column; Deep-travel seat track; Raised header and visor</t>
+  </si>
+  <si>
     <t>Yes</t>
   </si>
   <si>
-    <t>H</t>
-  </si>
-  <si>
-    <t>Power-adjustable pedal set; Extended-range seat riser; Tilt-telescope steering column; Deep-travel seat track; Raised header and visor</t>
-  </si>
-  <si>
     <t>Bus operators counted</t>
   </si>
   <si>
@@ -116,13 +116,13 @@
     <t>Share fitted</t>
   </si>
   <si>
-    <t>each operator's probability that all five fit dimensions lie within the envelope, under the survey's within-sex normal distribution of the five given the operator's stature and weight at the latest DOT physical, averaged over the operators</t>
+    <t>each operator's probability that all five fit dimensions lie within the envelope, under the survey's within-sex normal distribution of the five given the operator's stature and weight at the latest DOT physical, its eye height raised by how far the 140 operators Halvard measured in August 2026 sit above the survey's eye height for their own stature and weight (+28.0 mm for men, +27.6 mm for women), averaged over the operators</t>
   </si>
   <si>
     <t>Nearest cheaper configuration</t>
   </si>
   <si>
-    <t>E, 93.2 per cent; F, the next price down, 92.9 per cent</t>
+    <t>G, the next price down, 93.0 per cent</t>
   </si>
   <si>
     <t>the price per bus plus twelve years of each option's maintenance at its 2021 to 2025 cost per bus-year (sheet Option maintenance)</t>
@@ -185,7 +185,7 @@
     <t>Standard ES-12, 3.1 to 3.3: a configuration fits an operator when all five fit dimensions (popliteal height, buttock-knee length, eye height sitting, thumb-tip reach, abdominal extension depth sitting) lie within its envelope; the Authority specifies the lowest-priced configuration that fits at least 95 per cent of its bus operators.</t>
   </si>
   <si>
-    <t>The fit dimensions are not measured on our operators. Their stature and weight are, at each DOT physical (Ostrander Occupational Health to June 2021, Fernhill Occupational Medicine since); heights in inches and weights in pounds are taken in millimetres and kilograms.</t>
+    <t>The fit dimensions are not measured on our operators, apart from the sitting eye height of the 140 Halvard measured at Ridgeway in August 2026. Their stature and weight are, at each DOT physical (Ostrander Occupational Health to June 2021, Fernhill Occupational Medicine since); heights in inches and weights in pounds are taken in millimetres and kilograms.</t>
   </si>
   <si>
     <t>Shares are compared with 95 per cent unrounded and shown to one decimal.</t>
@@ -673,7 +673,7 @@
         <v>0</v>
       </c>
       <c r="D6" s="7">
-        <v>0.794</v>
+        <v>0.776</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>11</v>
@@ -693,7 +693,7 @@
         <v>1850</v>
       </c>
       <c r="D7" s="7">
-        <v>0.823</v>
+        <v>0.803</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>11</v>
@@ -713,7 +713,7 @@
         <v>2350</v>
       </c>
       <c r="D8" s="7">
-        <v>0.901</v>
+        <v>0.879</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>11</v>
@@ -753,7 +753,7 @@
         <v>3300</v>
       </c>
       <c r="D10" s="7">
-        <v>0.9320000000000001</v>
+        <v>0.904</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>11</v>
@@ -773,7 +773,7 @@
         <v>3900</v>
       </c>
       <c r="D11" s="7">
-        <v>0.929</v>
+        <v>0.904</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>11</v>
@@ -783,42 +783,42 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
+      <c r="A12" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="11">
+      <c r="C12" s="6">
         <v>4450</v>
       </c>
-      <c r="D12" s="12">
-        <v>0.964</v>
-      </c>
-      <c r="E12" s="13" t="s">
+      <c r="D12" s="7">
+        <v>0.93</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="6">
+        <v>12130</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="F12" s="11">
-        <v>12130</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="B13" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="C13" s="11">
+        <v>5900</v>
+      </c>
+      <c r="D13" s="12">
+        <v>0.97</v>
+      </c>
+      <c r="E13" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="6">
-        <v>5900</v>
-      </c>
-      <c r="D13" s="7">
-        <v>0.972</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F13" s="6">
+      <c r="F13" s="11">
         <v>13904</v>
       </c>
     </row>
